--- a/sobras.xlsx
+++ b/sobras.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>cor</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>obs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -467,6 +472,7 @@
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -487,6 +493,7 @@
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -511,6 +518,63 @@
           <t xml:space="preserve">carvalho mel </t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">noce naturalle </t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1165</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cinza </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sobras.xlsx
+++ b/sobras.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,32 +549,82 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D6" t="n">
+        <v>18</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cinza </t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D7" t="n">
+        <v>18</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>2750</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1850</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cinza </t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>beton</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/sobras.xlsx
+++ b/sobras.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,32 +599,124 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D8" t="n">
+        <v>18</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>beton</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2750</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1345</v>
+      </c>
+      <c r="C10" t="n">
+        <v>312</v>
+      </c>
+      <c r="D10" t="n">
+        <v>15</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>NÃO</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1568</v>
+      </c>
+      <c r="C11" t="n">
+        <v>284</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>arthur</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>jade</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>sem veio</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>2750</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>1850</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
         <is>
           <t>NÃO</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>beton</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
